--- a/data/trans_dic/IP19C04-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP19C04-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por extracción de algún diente o muela</t>
+          <t>Menores que en su última visita al dentista fue por extracción de algún diente o muela (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 11,03</t>
+          <t>0,96; 10,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,51</t>
+          <t>0,0; 8,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,98</t>
+          <t>0,0; 14,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,67; 11,18</t>
+          <t>2,45; 12,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 11,36</t>
+          <t>1,37; 11,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 12,53</t>
+          <t>1,41; 13,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,68</t>
+          <t>0,0; 5,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 8,23</t>
+          <t>1,44; 8,13</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 6,67</t>
+          <t>0,73; 6,81</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,82</t>
+          <t>0,0; 5,69</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 6,46</t>
+          <t>1,71; 6,4</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 15,71</t>
+          <t>1,89; 15,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,17</t>
+          <t>0,0; 10,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,92</t>
+          <t>0,0; 7,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,13</t>
+          <t>0,0; 5,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 15,91</t>
+          <t>1,72; 15,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 11,3</t>
+          <t>1,2; 10,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,68</t>
+          <t>0,0; 6,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 12,19</t>
+          <t>2,72; 12,15</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,81</t>
+          <t>0,0; 4,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 7,23</t>
+          <t>1,16; 7,07</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,48</t>
+          <t>0,54; 4,74</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 16,84</t>
+          <t>1,89; 16,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,91; 21,27</t>
+          <t>4,1; 23,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,27</t>
+          <t>0,0; 13,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 14,46</t>
+          <t>2,53; 14,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 15,36</t>
+          <t>1,79; 14,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,96</t>
+          <t>0,0; 11,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 20,18</t>
+          <t>1,99; 20,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,21; 12,18</t>
+          <t>2,59; 11,91</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 7,45</t>
+          <t>0,87; 7,61</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 13,73</t>
+          <t>2,89; 13,84</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 11,51</t>
+          <t>1,17; 11,93</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,96; 11,55</t>
+          <t>2,92; 11,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,62; 14,53</t>
+          <t>4,49; 14,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 9,53</t>
+          <t>2,55; 9,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 8,97</t>
+          <t>1,99; 9,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,04; 11,66</t>
+          <t>2,92; 11,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,46; 13,06</t>
+          <t>3,56; 13,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 7,62</t>
+          <t>1,32; 7,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 8,23</t>
+          <t>1,77; 8,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,79; 9,37</t>
+          <t>3,8; 9,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,82; 11,55</t>
+          <t>5,0; 11,69</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,75; 7,67</t>
+          <t>2,73; 7,26</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,6; 7,66</t>
+          <t>2,68; 7,36</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,03</t>
+          <t>0,0; 9,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,44; 18,94</t>
+          <t>7,17; 19,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,12; 13,77</t>
+          <t>3,09; 13,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,14; 12,79</t>
+          <t>2,18; 12,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,93; 15,33</t>
+          <t>3,98; 14,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,56; 14,2</t>
+          <t>2,8; 13,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,95</t>
+          <t>0,0; 8,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,76</t>
+          <t>0,0; 5,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,96; 10,0</t>
+          <t>3,06; 10,1</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,17; 14,26</t>
+          <t>6,48; 14,43</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,16; 8,13</t>
+          <t>2,26; 8,39</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 6,07</t>
+          <t>1,12; 6,12</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,34; 13,58</t>
+          <t>1,33; 12,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,73</t>
+          <t>0,0; 17,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,83</t>
+          <t>0,0; 10,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,9; 22,3</t>
+          <t>0,9; 21,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,83; 16,43</t>
+          <t>1,84; 16,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,63; 12,82</t>
+          <t>1,63; 14,3</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,17; 26,45</t>
+          <t>6,52; 29,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,02</t>
+          <t>0,0; 12,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,46; 11,27</t>
+          <t>2,7; 11,07</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,03; 11,55</t>
+          <t>2,01; 10,76</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,48; 16,15</t>
+          <t>3,41; 15,19</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,51; 14,43</t>
+          <t>1,93; 13,59</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,35; 7,4</t>
+          <t>3,47; 7,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,36; 8,85</t>
+          <t>4,54; 9,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,59; 7,52</t>
+          <t>3,46; 7,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,11; 6,93</t>
+          <t>3,22; 7,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,58; 9,04</t>
+          <t>4,78; 9,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,71; 8,2</t>
+          <t>3,61; 7,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,5; 6,03</t>
+          <t>2,42; 5,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,59</t>
+          <t>1,67; 4,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,6; 7,53</t>
+          <t>4,68; 7,57</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,5; 7,57</t>
+          <t>4,54; 7,52</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,41; 5,95</t>
+          <t>3,45; 5,96</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,71; 5,05</t>
+          <t>2,7; 5,0</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por extracción de algún diente o muela (tasa de respuesta: 99,51%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2096</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1662</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4320</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2087</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1861</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1723</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>4183</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2536</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1662</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>6042</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>527; 5724</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4118</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 6038</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1758; 8695</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>678; 5564</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>576; 5522</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5425</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1496; 8465</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>649; 6073</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5324</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2863; 10735</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2814</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1548</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1296</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1093</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2177</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2259</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1528</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>4991</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1548</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3555</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2621</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>764; 6369</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5028</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3962</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3378</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>637; 5790</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>647; 5800</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4890</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2111; 9425</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4737</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>1274; 7762</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>720; 6365</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2164</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>3545</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2549</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1289</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2491</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>5708</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2549</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4593</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3208</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>662; 5830</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1277; 7222</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3752</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1352; 7558</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>710; 5928</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3900</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>722; 7365</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2292; 10529</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>710; 6203</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1907; 9146</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>750; 7659</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>6128</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7924</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6156</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5433</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>6028</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>7022</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4009</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>5354</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>12157</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>14946</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>10165</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>10787</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2866; 11066</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>4095; 13506</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2837; 10735</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2209; 10560</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2811; 11346</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>3491; 13029</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1376; 8085</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2254; 11056</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>7378; 19039</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>9455; 22108</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5874; 15599</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>6394; 17543</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1555</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>10170</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4780</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>4029</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>5948</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>5378</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1654</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1224</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>7503</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>15548</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>6434</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>5253</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5189</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>5892; 16249</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2155; 9340</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1491; 8423</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2786; 10467</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2064; 10080</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5900</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5507</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>3819; 12599</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>10102; 22503</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3233; 12026</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>1924; 10500</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1920</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1293</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2788</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2579</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>4507</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1785</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>4499</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>3288</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5194</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>4574</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>532; 5170</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4563</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3450</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>404; 9597</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>659; 5863</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>610; 5363</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2099; 9453</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5505</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>2041; 8386</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>1268; 6802</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2208; 9840</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>1719; 12091</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>16678</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>21611</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>17885</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>18379</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>22364</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>18803</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>13718</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>39042</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>40414</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>31604</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>32485</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>11211; 23996</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>15282; 30618</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>11881; 26024</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>12450; 27708</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>16343; 31411</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>12362; 26358</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>8443; 20900</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>7976; 21331</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>31126; 50300</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>30859; 51097</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>23868; 41246</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>23405; 43267</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C04-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP19C04-Clase-trans_dic.xlsx
@@ -717,32 +717,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 10,45</t>
+          <t>0,96; 11,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,54</t>
+          <t>0,0; 7,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,04</t>
+          <t>0,0; 13,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 12,11</t>
+          <t>2,55; 11,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 11,27</t>
+          <t>1,37; 11,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 13,51</t>
+          <t>1,41; 12,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -752,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,65</t>
+          <t>0,0; 6,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 8,13</t>
+          <t>1,75; 8,2</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,81</t>
+          <t>0,68; 6,07</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,69</t>
+          <t>0,0; 6,06</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 6,4</t>
+          <t>1,64; 7,03</t>
         </is>
       </c>
     </row>
@@ -857,27 +857,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 15,73</t>
+          <t>1,83; 16,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,59</t>
+          <t>0,0; 11,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,11</t>
+          <t>0,0; 7,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,39</t>
+          <t>0,0; 5,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 15,63</t>
+          <t>1,74; 16,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -887,32 +887,32 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 10,73</t>
+          <t>1,17; 10,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,83</t>
+          <t>0,0; 8,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,72; 12,15</t>
+          <t>2,86; 12,35</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,71</t>
+          <t>0,0; 5,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 7,07</t>
+          <t>1,21; 6,68</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,74</t>
+          <t>0,53; 5,14</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 16,65</t>
+          <t>1,83; 16,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1007,52 +1007,52 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,1; 23,2</t>
+          <t>4,07; 23,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,44</t>
+          <t>0,0; 13,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 14,16</t>
+          <t>2,54; 14,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,79; 14,9</t>
+          <t>1,58; 15,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,16</t>
+          <t>0,0; 11,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 20,31</t>
+          <t>1,96; 18,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 11,91</t>
+          <t>3,15; 12,44</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 7,61</t>
+          <t>0,89; 7,72</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,89; 13,84</t>
+          <t>3,07; 13,91</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 11,93</t>
+          <t>1,22; 12,01</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,92; 11,28</t>
+          <t>2,85; 12,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,49; 14,8</t>
+          <t>4,72; 14,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,55; 9,66</t>
+          <t>2,77; 9,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 9,51</t>
+          <t>2,18; 9,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,92; 11,8</t>
+          <t>3,08; 11,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,56; 13,3</t>
+          <t>3,53; 13,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 7,78</t>
+          <t>1,79; 8,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,77; 8,68</t>
+          <t>1,85; 8,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,8; 9,8</t>
+          <t>3,89; 9,64</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,0; 11,69</t>
+          <t>4,92; 11,72</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,73; 7,26</t>
+          <t>2,66; 7,25</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,68; 7,36</t>
+          <t>2,54; 7,82</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,49</t>
+          <t>0,0; 10,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,17; 19,76</t>
+          <t>7,26; 19,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,09; 13,39</t>
+          <t>2,98; 12,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 12,3</t>
+          <t>2,31; 12,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,98; 14,95</t>
+          <t>4,01; 14,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,8; 13,68</t>
+          <t>3,17; 14,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,02</t>
+          <t>0,0; 7,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,34</t>
+          <t>0,0; 5,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,06; 10,1</t>
+          <t>3,14; 10,72</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,48; 14,43</t>
+          <t>6,63; 14,97</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,26; 8,39</t>
+          <t>2,11; 8,23</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 6,12</t>
+          <t>1,37; 6,35</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,33; 12,93</t>
+          <t>1,33; 13,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,76</t>
+          <t>0,0; 15,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,58</t>
+          <t>0,0; 9,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,9; 21,39</t>
+          <t>0,9; 21,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,84; 16,41</t>
+          <t>1,83; 16,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,63; 14,3</t>
+          <t>1,63; 14,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,52; 29,37</t>
+          <t>5,13; 26,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,47</t>
+          <t>0,0; 13,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,7; 11,07</t>
+          <t>2,55; 11,67</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,01; 10,76</t>
+          <t>2,0; 11,04</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,41; 15,19</t>
+          <t>3,41; 15,09</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,93; 13,59</t>
+          <t>1,47; 13,91</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,47; 7,43</t>
+          <t>3,38; 7,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,54; 9,1</t>
+          <t>4,53; 8,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,46; 7,58</t>
+          <t>3,46; 7,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,22; 7,16</t>
+          <t>3,1; 6,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,78; 9,19</t>
+          <t>4,58; 9,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,61; 7,69</t>
+          <t>3,67; 7,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,99</t>
+          <t>2,29; 5,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,46</t>
+          <t>1,72; 4,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,68; 7,57</t>
+          <t>4,56; 7,46</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,54; 7,52</t>
+          <t>4,43; 7,43</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,45; 5,96</t>
+          <t>3,46; 6,19</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,7; 5,0</t>
+          <t>2,79; 5,11</t>
         </is>
       </c>
     </row>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>527; 5724</t>
+          <t>524; 6070</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4118</t>
+          <t>0; 3460</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6038</t>
+          <t>0; 5959</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1758; 8695</t>
+          <t>1827; 8271</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>678; 5564</t>
+          <t>674; 5590</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>576; 5522</t>
+          <t>578; 5171</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1962,27 +1962,27 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5425</t>
+          <t>0; 6006</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1496; 8465</t>
+          <t>1822; 8537</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>649; 6073</t>
+          <t>610; 5412</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 5324</t>
+          <t>0; 5666</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2863; 10735</t>
+          <t>2757; 11796</t>
         </is>
       </c>
     </row>
@@ -2135,27 +2135,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>764; 6369</t>
+          <t>740; 6712</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5028</t>
+          <t>0; 5268</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3962</t>
+          <t>0; 4136</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3378</t>
+          <t>0; 3706</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>637; 5790</t>
+          <t>646; 6240</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2165,32 +2165,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>647; 5800</t>
+          <t>633; 5931</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4890</t>
+          <t>0; 5792</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2111; 9425</t>
+          <t>2217; 9580</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 4737</t>
+          <t>0; 5355</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1274; 7762</t>
+          <t>1329; 7329</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>720; 6365</t>
+          <t>712; 6899</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>662; 5830</t>
+          <t>639; 5750</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2353,52 +2353,52 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1277; 7222</t>
+          <t>1267; 7305</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3752</t>
+          <t>0; 3816</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1352; 7558</t>
+          <t>1357; 7473</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>710; 5928</t>
+          <t>630; 5967</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3900</t>
+          <t>0; 4024</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>722; 7365</t>
+          <t>709; 6674</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2292; 10529</t>
+          <t>2783; 10996</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>710; 6203</t>
+          <t>727; 6295</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1907; 9146</t>
+          <t>2031; 9190</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>750; 7659</t>
+          <t>785; 7706</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2866; 11066</t>
+          <t>2794; 11773</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4095; 13506</t>
+          <t>4305; 13336</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2837; 10735</t>
+          <t>3079; 11074</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2209; 10560</t>
+          <t>2416; 10780</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2811; 11346</t>
+          <t>2964; 11454</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3491; 13029</t>
+          <t>3459; 13240</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1376; 8085</t>
+          <t>1862; 8462</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2254; 11056</t>
+          <t>2356; 11026</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7378; 19039</t>
+          <t>7556; 18731</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9455; 22108</t>
+          <t>9312; 22183</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5874; 15599</t>
+          <t>5721; 15581</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6394; 17543</t>
+          <t>6068; 18640</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5189</t>
+          <t>0; 5478</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5892; 16249</t>
+          <t>5967; 15719</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2155; 9340</t>
+          <t>2081; 8965</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1491; 8423</t>
+          <t>1582; 8514</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2786; 10467</t>
+          <t>2807; 9928</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2064; 10080</t>
+          <t>2335; 10543</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 5900</t>
+          <t>0; 5666</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 5507</t>
+          <t>0; 5634</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3819; 12599</t>
+          <t>3919; 13366</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10102; 22503</t>
+          <t>10340; 23340</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3233; 12026</t>
+          <t>3025; 11802</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1924; 10500</t>
+          <t>2344; 10895</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>532; 5170</t>
+          <t>532; 5377</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4563</t>
+          <t>0; 3994</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3450</t>
+          <t>0; 3136</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>404; 9597</t>
+          <t>404; 9469</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>659; 5863</t>
+          <t>653; 5910</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>610; 5363</t>
+          <t>610; 5321</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2099; 9453</t>
+          <t>1650; 8409</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 5505</t>
+          <t>0; 6132</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2041; 8386</t>
+          <t>1931; 8838</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1268; 6802</t>
+          <t>1266; 6978</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2208; 9840</t>
+          <t>2207; 9779</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1719; 12091</t>
+          <t>1306; 12376</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>11211; 23996</t>
+          <t>10933; 24047</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>15282; 30618</t>
+          <t>15248; 30093</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11881; 26024</t>
+          <t>11873; 25290</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12450; 27708</t>
+          <t>11992; 26889</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>16343; 31411</t>
+          <t>15652; 30803</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12362; 26358</t>
+          <t>12573; 27066</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8443; 20900</t>
+          <t>8004; 20445</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>7976; 21331</t>
+          <t>8219; 22142</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>31126; 50300</t>
+          <t>30340; 49579</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>30859; 51097</t>
+          <t>30116; 50467</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23868; 41246</t>
+          <t>23933; 42854</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>23405; 43267</t>
+          <t>24132; 44224</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C04-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP19C04-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,23%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,55%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>3,83%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1,4%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3,86%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,23%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 11,08</t>
+          <t>1,37; 11,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,17</t>
+          <t>1,41; 12,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,55; 11,52</t>
+          <t>0,0; 6,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 11,33</t>
+          <t>0,95; 11,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 12,65</t>
+          <t>0,0; 8,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 12,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,25</t>
+          <t>2,52; 10,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 8,2</t>
+          <t>1,44; 8,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,07</t>
+          <t>0,75; 6,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,06</t>
+          <t>0,0; 5,82</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 7,03</t>
+          <t>1,74; 6,63</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5,88%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4,18%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>6,95%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>3,26%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,33%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,88%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 16,57</t>
+          <t>1,75; 15,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,42</t>
+          <t>1,2; 11,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,91</t>
+          <t>0,0; 6,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 16,84</t>
+          <t>1,6; 15,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 10,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 10,98</t>
+          <t>0,0; 6,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,09</t>
+          <t>0,0; 6,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,86; 12,35</t>
+          <t>2,82; 12,19</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,33</t>
+          <t>0,0; 4,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 6,68</t>
+          <t>1,18; 7,23</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,14</t>
+          <t>0,43; 4,01</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6,64%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6,4%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6,5%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>6,18%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>10,62%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,64%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,4%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 16,42</t>
+          <t>2,53; 14,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>1,83; 15,36</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 12,96</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1,84; 19,19</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1,82; 16,84</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>4,07; 23,47</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 13,66</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>2,54; 14,0</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,58; 15,0</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,52</t>
+          <t>3,91; 21,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 18,41</t>
+          <t>0,0; 13,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,15; 12,44</t>
+          <t>3,21; 12,18</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 7,72</t>
+          <t>0,9; 7,45</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,07; 13,91</t>
+          <t>3,03; 13,73</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 12,01</t>
+          <t>1,13; 10,68</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6,27%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7,17%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3,86%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3,94%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>6,24%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>8,69%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5,54%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,27%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,17%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,86%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,85; 12,0</t>
+          <t>3,04; 11,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,72; 14,62</t>
+          <t>3,46; 13,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,77; 9,97</t>
+          <t>1,3; 7,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 9,71</t>
+          <t>1,64; 7,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,08; 11,91</t>
+          <t>2,96; 11,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,53; 13,52</t>
+          <t>4,62; 14,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,79; 8,15</t>
+          <t>2,54; 9,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 8,66</t>
+          <t>2,38; 9,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,89; 9,64</t>
+          <t>3,79; 9,37</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,92; 11,72</t>
+          <t>4,82; 11,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,66; 7,25</t>
+          <t>2,75; 7,67</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 7,82</t>
+          <t>2,63; 7,75</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>8,49%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7,3%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>2,85%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>12,37%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>6,85%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,88%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>8,49%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,3%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,02</t>
+          <t>3,93; 15,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,26; 19,12</t>
+          <t>3,56; 14,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,98; 12,85</t>
+          <t>0,0; 6,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,31; 12,43</t>
+          <t>0,0; 5,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,01; 14,18</t>
+          <t>0,0; 10,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,17; 14,31</t>
+          <t>7,44; 18,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,7</t>
+          <t>3,12; 13,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,46</t>
+          <t>2,36; 13,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,14; 10,72</t>
+          <t>2,96; 10,0</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,63; 14,97</t>
+          <t>6,17; 14,26</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,11; 8,23</t>
+          <t>2,16; 8,13</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 6,35</t>
+          <t>1,38; 6,66</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>7,22%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5,32%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4,24%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>5,03%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>2,11%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6,21%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5,32%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>14,0%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,33; 13,44</t>
+          <t>1,83; 16,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,55</t>
+          <t>1,63; 12,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,62</t>
+          <t>5,17; 26,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,9; 21,11</t>
+          <t>0,0; 12,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,83; 16,54</t>
+          <t>1,34; 13,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,63; 14,18</t>
+          <t>0,0; 15,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,13; 26,12</t>
+          <t>0,0; 10,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,89</t>
+          <t>0,7; 7,94</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,55; 11,67</t>
+          <t>2,46; 11,27</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,0; 11,04</t>
+          <t>2,03; 11,55</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,41; 15,09</t>
+          <t>3,48; 16,15</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,47; 13,91</t>
+          <t>0,99; 8,35</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6,55%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5,48%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3,93%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>5,16%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>6,42%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>5,21%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4,75%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6,55%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,93%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,38; 7,44</t>
+          <t>4,58; 9,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,53; 8,94</t>
+          <t>3,71; 8,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,46; 7,37</t>
+          <t>2,5; 6,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,1; 6,95</t>
+          <t>1,73; 4,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,58; 9,01</t>
+          <t>3,35; 7,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,67; 7,89</t>
+          <t>4,36; 8,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,86</t>
+          <t>3,59; 7,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,63</t>
+          <t>2,88; 6,3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,56; 7,46</t>
+          <t>4,6; 7,53</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,43; 7,43</t>
+          <t>4,5; 7,57</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,46; 6,19</t>
+          <t>3,41; 5,95</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,79; 5,11</t>
+          <t>2,51; 4,76</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1796,37 +1796,37 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2087</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1861</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>2096</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>675</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>1662</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4320</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2087</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1861</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>4087</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6042</t>
+          <t>5887</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>524; 6070</t>
+          <t>676; 5606</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3460</t>
+          <t>576; 5122</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5959</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1827; 8271</t>
+          <t>0; 5686</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>674; 5590</t>
+          <t>523; 6043</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>578; 5171</t>
+          <t>0; 4106</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 5583</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 6006</t>
+          <t>1801; 7655</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1822; 8537</t>
+          <t>1502; 8572</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>610; 5412</t>
+          <t>672; 5945</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 5666</t>
+          <t>0; 5441</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2757; 11796</t>
+          <t>2819; 10749</t>
         </is>
       </c>
     </row>
@@ -1999,37 +1999,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2177</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2259</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1261</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2814</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1548</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1296</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1093</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2177</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2259</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1528</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2621</t>
+          <t>2391</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>740; 6712</t>
+          <t>647; 5895</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5268</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4136</t>
+          <t>650; 6105</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3706</t>
+          <t>0; 4610</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>646; 6240</t>
+          <t>648; 6363</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4829</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>633; 5931</t>
+          <t>0; 3856</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5792</t>
+          <t>0; 3928</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2217; 9580</t>
+          <t>2185; 9455</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 5355</t>
+          <t>0; 4833</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1329; 7329</t>
+          <t>1299; 7939</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>712; 6899</t>
+          <t>582; 5435</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,54 +2275,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3545</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2549</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1289</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2242</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>2164</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>3304</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>716</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>3545</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>751</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>5708</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>2549</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1289</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2491</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>5708</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2549</t>
-        </is>
-      </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
           <t>4593</t>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>2993</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>639; 5750</t>
+          <t>1351; 7716</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>728; 6112</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4529</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>635; 6620</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>638; 5896</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1267; 7305</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3816</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1357; 7473</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>630; 5967</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4024</t>
+          <t>1218; 6620</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>709; 6674</t>
+          <t>0; 3884</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2783; 10996</t>
+          <t>2836; 10768</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>727; 6295</t>
+          <t>730; 6071</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2031; 9190</t>
+          <t>1999; 9069</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>785; 7706</t>
+          <t>720; 6785</t>
         </is>
       </c>
     </row>
@@ -2420,37 +2420,37 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>6028</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7022</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4009</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4818</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>6128</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>7924</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>6156</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5433</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6028</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7022</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4009</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5354</t>
+          <t>5714</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10787</t>
+          <t>10533</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2794; 11773</t>
+          <t>2923; 11212</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4305; 13336</t>
+          <t>3390; 12795</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3079; 11074</t>
+          <t>1349; 7915</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2416; 10780</t>
+          <t>2007; 9607</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2964; 11454</t>
+          <t>2906; 11331</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3459; 13240</t>
+          <t>4214; 13257</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1862; 8462</t>
+          <t>2821; 10587</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2356; 11026</t>
+          <t>2592; 10307</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7556; 18731</t>
+          <t>7373; 18196</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9312; 22183</t>
+          <t>9117; 21860</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5721; 15581</t>
+          <t>5903; 16483</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6068; 18640</t>
+          <t>6092; 17937</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>5948</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5378</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1654</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>1555</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>10170</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>4780</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>4029</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>5948</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>5378</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1654</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>4295</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>5451</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5478</t>
+          <t>2750; 10739</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5967; 15719</t>
+          <t>2623; 10461</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2081; 8965</t>
+          <t>0; 5114</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1582; 8514</t>
+          <t>0; 5016</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2807; 9928</t>
+          <t>0; 5483</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2335; 10543</t>
+          <t>6116; 15571</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 5666</t>
+          <t>2178; 9605</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 5634</t>
+          <t>1632; 9571</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3919; 13366</t>
+          <t>3686; 12469</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10340; 23340</t>
+          <t>9614; 22224</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3025; 11802</t>
+          <t>3094; 11651</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2344; 10895</t>
+          <t>2248; 10858</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2579</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4507</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1854</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>1920</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1293</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>687</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2788</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2579</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>4507</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4574</t>
+          <t>3101</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>532; 5377</t>
+          <t>655; 5870</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3994</t>
+          <t>610; 4809</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3136</t>
+          <t>1663; 8514</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>404; 9469</t>
+          <t>0; 5589</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>653; 5910</t>
+          <t>536; 5433</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>610; 5321</t>
+          <t>0; 4040</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1650; 8409</t>
+          <t>0; 3529</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 6132</t>
+          <t>332; 3758</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1931; 8838</t>
+          <t>1861; 8538</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1266; 6978</t>
+          <t>1280; 7300</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2207; 9779</t>
+          <t>2254; 10465</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1306; 12376</t>
+          <t>904; 7610</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>22364</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>18803</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>13718</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>13133</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>16678</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>21611</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>17885</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>18379</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>22364</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>18803</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>13718</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>14105</t>
+          <t>17224</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>32485</t>
+          <t>30356</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>10933; 24047</t>
+          <t>15666; 30885</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>15248; 30093</t>
+          <t>12712; 28115</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11873; 25290</t>
+          <t>8740; 21051</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11992; 26889</t>
+          <t>7882; 20592</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>15652; 30803</t>
+          <t>10830; 23901</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12573; 27066</t>
+          <t>14672; 29792</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8004; 20445</t>
+          <t>12314; 25810</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>8219; 22142</t>
+          <t>11261; 24633</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>30340; 49579</t>
+          <t>30585; 50037</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>30116; 50467</t>
+          <t>30562; 51449</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23933; 42854</t>
+          <t>23623; 41173</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>24132; 44224</t>
+          <t>21240; 40304</t>
         </is>
       </c>
     </row>
